--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2411.39</v>
+        <v>2457.24</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>17775.25</v>
+        <v>17511.89</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9279.51</v>
+        <v>9367.66</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2442.08</v>
+        <v>2451.58</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2832.43</v>
+        <v>2838.46</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4061.36</v>
+        <v>4070.68</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3354.09</v>
+        <v>3300.31</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>20550.59</v>
+        <v>20449.55</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10211.24</v>
+        <v>10161.04</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2258-5597-CM26</t>
+          <t>2258-5681-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>20449.55</v>
+        <v>10161.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2258-5681-CM26</t>
+          <t>2258-5597-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,7 +1057,556 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10161.04</v>
+        <v>20449.55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3391-522-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>5440.67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3391-527-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>2973.18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3391-543-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>3548.94</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2258-6314-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>22308.77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2258-6335-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>60794</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2258-6605-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>5517.44</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2215-870-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.606.202-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ARENYS MED S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>16369.14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3391-549-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>2585.36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3391-550-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>4086.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Spinex Corporation Chile S.A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2258-5681-CM26</t>
+          <t>2258-5597-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10161.04</v>
+        <v>20449.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2258-5597-CM26</t>
+          <t>2258-5681-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>20449.55</v>
+        <v>10161.04</v>
       </c>
     </row>
     <row r="11">
@@ -1607,6 +1607,189 @@
       </c>
       <c r="M19" s="2" t="n">
         <v>4086.47</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3391-551-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>4186.71</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2258-7186-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>22225.28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2258-7398-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>18783.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
@@ -562,7 +562,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +932,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2258-5597-CM26</t>
+          <t>2258-5681-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>20449.55</v>
+        <v>10161.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2258-5681-CM26</t>
+          <t>2258-5597-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10161.04</v>
+        <v>20449.55</v>
       </c>
     </row>
     <row r="11">
@@ -1254,7 +1254,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2258-6314-CM26</t>
+          <t>2258-6335-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>22308.77</v>
+        <v>60794</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2258-6335-CM26</t>
+          <t>2258-6314-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>60794</v>
+        <v>22308.77</v>
       </c>
     </row>
     <row r="16">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1798,6 +1798,315 @@
       </c>
       <c r="M22" s="2" t="n">
         <v>18783.26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2258-7911-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>2544.74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2258-7631-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>14857.81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2258-7617-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>3657.63</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2258-7501-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>8641.85</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2258-8238-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>20409.08</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1254,7 +1254,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2258-6335-CM26</t>
+          <t>2258-6314-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>60794</v>
+        <v>22308.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2258-6314-CM26</t>
+          <t>2258-6605-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>22308.77</v>
+        <v>5517.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2258-6605-CM26</t>
+          <t>2258-6335-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5517.44</v>
+        <v>60794</v>
       </c>
     </row>
     <row r="17">
@@ -2107,6 +2107,67 @@
       </c>
       <c r="M27" s="2" t="n">
         <v>20409.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3391-586-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.101.086-9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>4513.02</v>
       </c>
     </row>
   </sheetData>
